--- a/artfynd/A 18576-2026 artfynd.xlsx
+++ b/artfynd/A 18576-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133596764</v>
       </c>
       <c r="B2" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133596760</v>
+        <v>133596772</v>
       </c>
       <c r="B3" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658435</v>
+        <v>658381</v>
       </c>
       <c r="R3" t="n">
-        <v>6630336</v>
+        <v>6630364</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133596772</v>
+        <v>133596760</v>
       </c>
       <c r="B4" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658381</v>
+        <v>658435</v>
       </c>
       <c r="R4" t="n">
-        <v>6630364</v>
+        <v>6630336</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>133596771</v>
       </c>
       <c r="B5" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133596766</v>
       </c>
       <c r="B6" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18576-2026 artfynd.xlsx
+++ b/artfynd/A 18576-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133596764</v>
+        <v>133596761</v>
       </c>
       <c r="B2" t="n">
-        <v>101396</v>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658439</v>
+        <v>658435</v>
       </c>
       <c r="R2" t="n">
-        <v>6630328</v>
+        <v>6630336</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133596772</v>
+        <v>133596769</v>
       </c>
       <c r="B3" t="n">
-        <v>101396</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658381</v>
+        <v>658440</v>
       </c>
       <c r="R3" t="n">
-        <v>6630364</v>
+        <v>6630356</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>133596760</v>
       </c>
       <c r="B4" t="n">
-        <v>101396</v>
+        <v>101403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133596771</v>
+        <v>133596764</v>
       </c>
       <c r="B5" t="n">
-        <v>101396</v>
+        <v>101403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>658440</v>
+        <v>658439</v>
       </c>
       <c r="R5" t="n">
-        <v>6630353</v>
+        <v>6630328</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>133596766</v>
       </c>
       <c r="B6" t="n">
-        <v>101396</v>
+        <v>101403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,6 +1207,220 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133596771</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenby, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>658440</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6630353</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133596772</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenby, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>658381</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6630364</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18576-2026 artfynd.xlsx
+++ b/artfynd/A 18576-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133596761</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133596769</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133596760</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133596764</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133596766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133596771</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,8 +1456,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133596772</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>